--- a/استلاف.xlsx
+++ b/استلاف.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\5dmt Shashat\Codes and Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681F7CAA-41D3-49F6-B8DC-F2CEB34B755F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321DA75D-1096-4425-B8BA-63010A98FE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1837,7 +1840,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="10">
-        <f t="shared" ref="B3:B50" si="0">COUNTA(C3:AC3)</f>
+        <f>COUNTA(C3:AC3)</f>
         <v>24</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -1921,7 +1924,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C4:AC4)</f>
         <v>20</v>
       </c>
       <c r="C4" s="8" t="s">
@@ -1997,8 +2000,8 @@
         <v>52</v>
       </c>
       <c r="B5" s="10">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>COUNTA(C5:AC5)</f>
+        <v>18</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>51</v>
@@ -2046,17 +2049,16 @@
         <v>261</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>324</v>
+        <v>66</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="U5" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
       <c r="Y5" s="5"/>
@@ -2070,7 +2072,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C6:AC6)</f>
         <v>17</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -2140,7 +2142,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C7:AC7)</f>
         <v>15</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -2270,7 +2272,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C9:AC9)</f>
         <v>14</v>
       </c>
       <c r="C9" s="8" t="s">
@@ -2396,7 +2398,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C11:AC11)</f>
         <v>13</v>
       </c>
       <c r="C11" s="8" t="s">
@@ -2458,7 +2460,7 @@
         <v>31</v>
       </c>
       <c r="B12" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C12:AC12)</f>
         <v>11</v>
       </c>
       <c r="C12" s="8" t="s">
@@ -2516,7 +2518,7 @@
         <v>33</v>
       </c>
       <c r="B13" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C13:AC13)</f>
         <v>10</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -2572,7 +2574,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C14:AC14)</f>
         <v>10</v>
       </c>
       <c r="C14" s="14" t="s">
@@ -2628,7 +2630,7 @@
         <v>57</v>
       </c>
       <c r="B15" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C15:AC15)</f>
         <v>10</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -2684,7 +2686,7 @@
         <v>81</v>
       </c>
       <c r="B16" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C16:AC16)</f>
         <v>9</v>
       </c>
       <c r="C16" s="8" t="s">
@@ -2738,7 +2740,7 @@
         <v>94</v>
       </c>
       <c r="B17" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C17:AC17)</f>
         <v>9</v>
       </c>
       <c r="C17" s="8" t="s">
@@ -2792,7 +2794,7 @@
         <v>76</v>
       </c>
       <c r="B18" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C18:AC18)</f>
         <v>8</v>
       </c>
       <c r="C18" s="14" t="s">
@@ -2844,7 +2846,7 @@
         <v>74</v>
       </c>
       <c r="B19" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C19:AC19)</f>
         <v>7</v>
       </c>
       <c r="C19" s="8" t="s">
@@ -2894,7 +2896,7 @@
         <v>71</v>
       </c>
       <c r="B20" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C20:AC20)</f>
         <v>7</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -2944,7 +2946,7 @@
         <v>36</v>
       </c>
       <c r="B21" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C21:AC21)</f>
         <v>7</v>
       </c>
       <c r="C21" s="8" t="s">
@@ -2994,7 +2996,7 @@
         <v>54</v>
       </c>
       <c r="B22" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C22:AC22)</f>
         <v>6</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -3042,7 +3044,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C23:AC23)</f>
         <v>6</v>
       </c>
       <c r="C23" s="8" t="s">
@@ -3090,7 +3092,7 @@
         <v>58</v>
       </c>
       <c r="B24" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C24:AC24)</f>
         <v>6</v>
       </c>
       <c r="C24" s="8" t="s">
@@ -3138,7 +3140,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C25:AC25)</f>
         <v>5</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -3184,7 +3186,7 @@
         <v>157</v>
       </c>
       <c r="B26" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C26:AC26)</f>
         <v>5</v>
       </c>
       <c r="C26" s="14" t="s">
@@ -3230,7 +3232,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C27:AC27)</f>
         <v>5</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -3276,7 +3278,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C28:AC28)</f>
         <v>5</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -3322,7 +3324,7 @@
         <v>152</v>
       </c>
       <c r="B29" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C29:AC29)</f>
         <v>5</v>
       </c>
       <c r="C29" s="14" t="s">
@@ -3368,7 +3370,7 @@
         <v>132</v>
       </c>
       <c r="B30" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C30:AC30)</f>
         <v>3</v>
       </c>
       <c r="C30" s="14" t="s">
@@ -3410,7 +3412,7 @@
         <v>143</v>
       </c>
       <c r="B31" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C31:AC31)</f>
         <v>3</v>
       </c>
       <c r="C31" s="14" t="s">
@@ -3452,7 +3454,7 @@
         <v>60</v>
       </c>
       <c r="B32" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C32:AC32)</f>
         <v>3</v>
       </c>
       <c r="C32" s="14" t="s">
@@ -3491,19 +3493,21 @@
     </row>
     <row r="33" spans="1:29" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A33" s="7" t="s">
-        <v>164</v>
+        <v>275</v>
       </c>
       <c r="B33" s="10">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTA(C33:AC33)</f>
+        <v>3</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>164</v>
+        <v>275</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E33" s="5"/>
+        <v>362</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>323</v>
+      </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -3531,17 +3535,17 @@
     </row>
     <row r="34" spans="1:29" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A34" s="7" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="B34" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C34:AC34)</f>
         <v>2</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>310</v>
+        <v>205</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -3571,17 +3575,17 @@
     </row>
     <row r="35" spans="1:29" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A35" s="7" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="B35" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C35:AC35)</f>
         <v>2</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>172</v>
+        <v>310</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -3611,17 +3615,17 @@
     </row>
     <row r="36" spans="1:29" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A36" s="7" t="s">
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="B36" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C36:AC36)</f>
         <v>2</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>362</v>
+        <v>172</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -3654,7 +3658,7 @@
         <v>89</v>
       </c>
       <c r="B37" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C37:AC37)</f>
         <v>2</v>
       </c>
       <c r="C37" s="14" t="s">
@@ -3694,7 +3698,7 @@
         <v>83</v>
       </c>
       <c r="B38" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C38:AC38)</f>
         <v>2</v>
       </c>
       <c r="C38" s="14" t="s">
@@ -3734,7 +3738,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C39:AC39)</f>
         <v>2</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -3774,7 +3778,7 @@
         <v>185</v>
       </c>
       <c r="B40" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C40:AC40)</f>
         <v>2</v>
       </c>
       <c r="C40" s="8" t="s">
@@ -3814,7 +3818,7 @@
         <v>123</v>
       </c>
       <c r="B41" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C41:AC41)</f>
         <v>2</v>
       </c>
       <c r="C41" s="14" t="s">
@@ -3854,7 +3858,7 @@
         <v>120</v>
       </c>
       <c r="B42" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C42:AC42)</f>
         <v>2</v>
       </c>
       <c r="C42" s="14" t="s">
@@ -3894,7 +3898,7 @@
         <v>50</v>
       </c>
       <c r="B43" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C43:AC43)</f>
         <v>2</v>
       </c>
       <c r="C43" s="8" t="s">
@@ -3934,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="B44" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C44:AC44)</f>
         <v>1</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -3972,7 +3976,7 @@
         <v>20</v>
       </c>
       <c r="B45" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C45:AC45)</f>
         <v>1</v>
       </c>
       <c r="C45" s="8" t="s">
@@ -4010,7 +4014,7 @@
         <v>229</v>
       </c>
       <c r="B46" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C46:AC46)</f>
         <v>1</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -4048,7 +4052,7 @@
         <v>241</v>
       </c>
       <c r="B47" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C47:AC47)</f>
         <v>1</v>
       </c>
       <c r="C47" s="8" t="s">
@@ -4086,7 +4090,7 @@
         <v>112</v>
       </c>
       <c r="B48" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C48:AC48)</f>
         <v>1</v>
       </c>
       <c r="C48" s="8" t="s">
@@ -4124,7 +4128,7 @@
         <v>296</v>
       </c>
       <c r="B49" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C49:AC49)</f>
         <v>1</v>
       </c>
       <c r="C49" s="8" t="s">
@@ -4162,7 +4166,7 @@
         <v>286</v>
       </c>
       <c r="B50" s="10">
-        <f t="shared" si="0"/>
+        <f>COUNTA(C50:AC50)</f>
         <v>1</v>
       </c>
       <c r="C50" s="15" t="s">
@@ -4200,7 +4204,7 @@
         <v>337</v>
       </c>
       <c r="B51" s="10">
-        <f t="shared" ref="B51:B66" si="1">COUNTA(C51:AC51)</f>
+        <f>COUNTA(C51:AC51)</f>
         <v>1</v>
       </c>
       <c r="C51" s="8" t="s">
@@ -4238,7 +4242,7 @@
         <v>348</v>
       </c>
       <c r="B52" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C52:AC52)</f>
         <v>1</v>
       </c>
       <c r="C52" s="8" t="s">
@@ -4276,7 +4280,7 @@
         <v>360</v>
       </c>
       <c r="B53" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C53:AC53)</f>
         <v>1</v>
       </c>
       <c r="C53" s="8" t="s">
@@ -4314,7 +4318,7 @@
         <v>44</v>
       </c>
       <c r="B54" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C54:AC54)</f>
         <v>1</v>
       </c>
       <c r="C54" s="8" t="s">
@@ -4352,7 +4356,7 @@
         <v>140</v>
       </c>
       <c r="B55" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C55:AC55)</f>
         <v>1</v>
       </c>
       <c r="C55" s="8" t="s">
@@ -4390,7 +4394,7 @@
         <v>154</v>
       </c>
       <c r="B56" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C56:AC56)</f>
         <v>1</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -4428,7 +4432,7 @@
         <v>167</v>
       </c>
       <c r="B57" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C57:AC57)</f>
         <v>1</v>
       </c>
       <c r="C57" s="8" t="s">
@@ -4466,7 +4470,7 @@
         <v>179</v>
       </c>
       <c r="B58" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C58:AC58)</f>
         <v>1</v>
       </c>
       <c r="C58" s="8" t="s">
@@ -4504,7 +4508,7 @@
         <v>351</v>
       </c>
       <c r="B59" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C59:AC59)</f>
         <v>1</v>
       </c>
       <c r="C59" s="8" t="s">
@@ -4542,7 +4546,7 @@
         <v>322</v>
       </c>
       <c r="B60" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C60:AC60)</f>
         <v>1</v>
       </c>
       <c r="C60" s="8" t="s">
@@ -4580,7 +4584,7 @@
         <v>364</v>
       </c>
       <c r="B61" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C61:AC61)</f>
         <v>1</v>
       </c>
       <c r="C61" s="8" t="s">
@@ -4618,7 +4622,7 @@
         <v>228</v>
       </c>
       <c r="B62" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C62:AC62)</f>
         <v>1</v>
       </c>
       <c r="C62" s="8" t="s">
@@ -4656,7 +4660,7 @@
         <v>315</v>
       </c>
       <c r="B63" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C63:AC63)</f>
         <v>1</v>
       </c>
       <c r="C63" s="8" t="s">
@@ -4694,7 +4698,7 @@
         <v>325</v>
       </c>
       <c r="B64" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C64:AC64)</f>
         <v>1</v>
       </c>
       <c r="C64" s="8" t="s">
@@ -4732,7 +4736,7 @@
         <v>345</v>
       </c>
       <c r="B65" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C65:AC65)</f>
         <v>1</v>
       </c>
       <c r="C65" s="8" t="s">
@@ -4770,7 +4774,7 @@
         <v>356</v>
       </c>
       <c r="B66" s="10">
-        <f t="shared" si="1"/>
+        <f>COUNTA(C66:AC66)</f>
         <v>1</v>
       </c>
       <c r="C66" s="8" t="s">
@@ -4808,7 +4812,7 @@
         <v>366</v>
       </c>
       <c r="B67" s="10">
-        <f t="shared" ref="B67:B71" si="2">COUNTA(C67:AC67)</f>
+        <f>COUNTA(C67:AC67)</f>
         <v>1</v>
       </c>
       <c r="C67" s="8" t="s">
@@ -4846,7 +4850,7 @@
         <v>19</v>
       </c>
       <c r="B68" s="10">
-        <f t="shared" si="2"/>
+        <f>COUNTA(C68:AC68)</f>
         <v>1</v>
       </c>
       <c r="C68" s="8" t="s">
@@ -4884,7 +4888,7 @@
         <v>38</v>
       </c>
       <c r="B69" s="10">
-        <f t="shared" si="2"/>
+        <f>COUNTA(C69:AC69)</f>
         <v>1</v>
       </c>
       <c r="C69" s="8" t="s">
@@ -4922,7 +4926,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="10">
-        <f t="shared" si="2"/>
+        <f>COUNTA(C70:AC70)</f>
         <v>1</v>
       </c>
       <c r="C70" s="8" t="s">
@@ -4960,7 +4964,7 @@
         <v>98</v>
       </c>
       <c r="B71" s="10">
-        <f t="shared" si="2"/>
+        <f>COUNTA(C71:AC71)</f>
         <v>1</v>
       </c>
       <c r="C71" s="8" t="s">
@@ -5059,6 +5063,9 @@
       <c r="AC73" s="1"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC71">
+    <sortCondition descending="1" ref="B2:B71"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="C1:AC1"/>
   </mergeCells>
